--- a/04_DESIGN_TABLES/DesignTable_1601.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1601.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1247,24 +1252,71 @@
           <t>1601-02-02-02-FG</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.405</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>1601-02-02-02-FG</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1/8-27 (A NPTF) x 1/8-27 (A1 (2) NPSM) x 1/8-27 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1275,6 +1327,11 @@
       <c r="V12" t="inlineStr">
         <is>
           <t>1601-02-02-02-FG</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1284,24 +1341,71 @@
           <t>1601-04-04-04-FG</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.54</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>1601-04-04-04-FG</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF) x 1/4-18 (A1 (2) NPSM) x 1/4-18 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-04-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-04-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1312,6 +1416,11 @@
       <c r="V13" t="inlineStr">
         <is>
           <t>1601-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1321,24 +1430,71 @@
           <t>1601-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.675</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>1601-06-06-06-FG</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 3/8-18 (A1 (2) NPSM) x 3/8-18 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1349,6 +1505,11 @@
       <c r="V14" t="inlineStr">
         <is>
           <t>1601-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1358,24 +1519,71 @@
           <t>1601-08-08-08-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.84</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>1601-08-08-08-FG</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF) x 1/2-14 (A1 (2) NPSM) x 1/2-14 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1386,6 +1594,11 @@
       <c r="V15" t="inlineStr">
         <is>
           <t>1601-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1608,71 @@
           <t>1601-12-12-12-FG</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.05</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>1601-12-12-12-FG</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 3/4-14 (A1 (2) NPSM) x 3/4-14 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1423,6 +1683,11 @@
       <c r="V16" t="inlineStr">
         <is>
           <t>1601-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1432,24 +1697,71 @@
           <t>1601-16-16-16-FG</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.315</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>1601-16-16-16-FG</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A NPTF) x 1-11 1/2 (A1 (2) NPSM) x 1-11 1/2 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1601-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1601-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1460,6 +1772,11 @@
       <c r="V17" t="inlineStr">
         <is>
           <t>1601-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1469,24 +1786,71 @@
           <t>1601-20-20-20-FG</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.66</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>1601-20-20-20-FG</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A NPTF) x 1 1/4-11 1/2 (A1 (2) NPSM) x 1 1/4-11 1/2 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1497,6 +1861,11 @@
       <c r="V18" t="inlineStr">
         <is>
           <t>1601-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
